--- a/docs/safefill_timeline.xlsx
+++ b/docs/safefill_timeline.xlsx
@@ -1716,7 +1716,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5*B6</f>
-        <v>5400</v>
+        <v>3240</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
